--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,15 +440,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Image Link</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -482,10 +492,20 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -519,10 +539,20 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -556,10 +586,20 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Manual Fix</t>
         </is>
@@ -593,10 +633,20 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -630,10 +680,20 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Flagged</t>
         </is>
@@ -667,10 +727,20 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -704,10 +774,20 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -741,10 +821,20 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -778,10 +868,20 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -815,10 +915,20 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -852,10 +962,20 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -884,20 +1004,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Google Fit</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Flagged</t>
         </is>
@@ -926,20 +1051,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Strava</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>Flagged</t>
         </is>
@@ -968,20 +1098,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Strava</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1010,20 +1145,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Strava</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1057,15 +1197,20 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>Strava</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
       <c r="H17" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1094,20 +1239,166 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>105,386</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Garmin</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:28:49</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:07:38</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-20 18:54:02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6.03</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1124,7 +1415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1140,6 +1431,11 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Total Steps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Total Points</t>
         </is>
       </c>
@@ -1151,10 +1447,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51</v>
+        <v>64.86</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1169,6 +1468,9 @@
       <c r="C3" t="n">
         <v>0</v>
       </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1180,6 +1482,9 @@
         <v>20.06</v>
       </c>
       <c r="C4" t="n">
+        <v>105386</v>
+      </c>
+      <c r="D4" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1199,6 +1504,11 @@
           <t>---</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1207,10 +1517,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>75.84</v>
+        <v>89.7</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>105386</v>
+      </c>
+      <c r="D6" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,25 +440,15 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Image Link</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Image Link</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -492,20 +482,10 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -539,20 +519,10 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -586,20 +556,10 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>Manual Fix</t>
         </is>
@@ -633,20 +593,10 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -680,20 +630,10 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>Flagged</t>
         </is>
@@ -727,20 +667,10 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -774,20 +704,10 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -821,20 +741,10 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -868,20 +778,10 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -915,20 +815,10 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -962,20 +852,10 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1399,6 +1279,100 @@
         </is>
       </c>
       <c r="I21" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>5/20/2026 19:07:24</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>5/20/2026 19:19:30</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1447,13 +1421,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64.86</v>
+        <v>70.17</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1479,13 +1453,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.06</v>
+        <v>23.08</v>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
         <v>105386</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -1517,13 +1491,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>89.7</v>
+        <v>98.03</v>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
         <v>105386</v>
-      </c>
-      <c r="D6" t="n">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1373,6 +1373,53 @@
         </is>
       </c>
       <c r="I23" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>5/21/2026 18:56:16</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1421,7 +1468,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70.17</v>
+        <v>73.05</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1491,7 +1538,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>98.03</v>
+        <v>100.91</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1420,6 +1420,53 @@
         </is>
       </c>
       <c r="I24" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>5/22/2026 8:02:19</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1468,7 +1515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73.05</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1538,7 +1585,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100.91</v>
+        <v>104.9</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,15 +440,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Image Link</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -457,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-14 19:21:49</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -472,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -482,24 +492,34 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-14 19:59:35</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -519,24 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-14 20:34:20</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -546,7 +576,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -556,24 +586,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Manual Fix</t>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-14 23:28:39</t>
+          <t>2026-05-18 20:08:08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -583,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -593,10 +633,20 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -605,12 +655,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-16 14:00:21</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -620,7 +670,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -630,47 +680,67 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-16 17:39:10</t>
+          <t>2026-05-19 11:51:47</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105,386</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -679,7 +749,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-16 18:30:22</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -694,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -704,10 +774,20 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -716,7 +796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-17 09:37:57</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -726,12 +806,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -741,10 +821,20 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -753,22 +843,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-17 12:33:11</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -778,10 +868,20 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -790,22 +890,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-17 15:41:15</t>
+          <t>5/20/2026 19:07:24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cycling</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -815,10 +915,20 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -827,22 +937,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:21</t>
+          <t>5/20/2026 19:19:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -852,10 +962,20 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -864,7 +984,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>5/21/2026 18:56:16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -879,7 +999,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -889,12 +1009,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -904,19 +1024,19 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>5/22/2026 8:02:19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -926,7 +1046,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -936,7 +1056,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -951,19 +1071,19 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>5/23/2026 14:39:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -973,7 +1093,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -988,7 +1108,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -998,19 +1118,19 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Committee Approval Required</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-18 20:08:08</t>
+          <t>5/23/2026 18:20:55</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1020,22 +1140,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3,390</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1052,22 +1172,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-14 19:21:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1077,20 +1197,10 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1099,45 +1209,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-19 11:51:47</t>
+          <t>2026-05-14 19:59:35</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>105,386</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1146,12 +1246,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-14 20:34:20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1161,7 +1261,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1171,34 +1271,24 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Verified</t>
+          <t>Manual Fix</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-05-14 23:28:39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1208,7 +1298,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1218,20 +1308,10 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1240,22 +1320,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-05-16 14:00:21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1265,29 +1345,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5/20/2026 19:07:24</t>
+          <t>2026-05-16 17:39:10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1302,7 +1372,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1312,20 +1382,10 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1334,22 +1394,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5/20/2026 19:19:30</t>
+          <t>2026-05-16 18:30:22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1359,20 +1419,10 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1381,7 +1431,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5/21/2026 18:56:16</t>
+          <t>2026-05-17 09:37:57</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1391,12 +1441,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1406,20 +1456,10 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1428,22 +1468,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5/22/2026 8:02:19</t>
+          <t>2026-05-17 12:33:11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1453,20 +1493,84 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-17 15:41:15</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cycling</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4.78</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-17 16:46:21</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>7.07</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1515,13 +1619,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77.04000000000001</v>
+        <v>59.27</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3390</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -1531,7 +1635,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1547,13 +1651,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.08</v>
+        <v>4.42</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>105386</v>
       </c>
       <c r="D4" t="n">
-        <v>105386</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -1585,13 +1689,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>104.9</v>
+        <v>63.69</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>108776</v>
       </c>
       <c r="D6" t="n">
-        <v>105386</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-14 19:21:49</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,24 +482,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.54</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>View</t>
@@ -507,19 +499,19 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-14 19:59:35</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -529,24 +521,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>View</t>
@@ -554,19 +538,19 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-14 20:34:20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -576,24 +560,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.77</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>View</t>
@@ -601,19 +577,19 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Manual Fix</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18 20:08:08</t>
+          <t>2026-05-14 23:28:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -623,24 +599,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.14</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>5.62</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>View</t>
@@ -655,12 +623,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-16 14:00:21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -670,24 +638,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>View</t>
@@ -695,46 +655,38 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-19 11:51:47</t>
+          <t>2026-05-16 17:39:10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>105,386</t>
-        </is>
-      </c>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>View</t>
@@ -749,7 +701,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-16 18:30:22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -764,24 +716,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.97</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>View</t>
@@ -796,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-05-17 09:37:57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -806,29 +750,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>9.29</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>View</t>
@@ -843,39 +779,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-05-17 12:33:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6.03</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>5.91</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>View</t>
@@ -890,39 +818,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5/20/2026 19:07:24</t>
+          <t>2026-05-17 15:41:15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Cycling</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>4.78</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>View</t>
@@ -937,39 +857,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5/20/2026 19:19:30</t>
+          <t>2026-05-17 16:46:21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.02</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>7.07</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>View</t>
@@ -984,7 +896,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5/21/2026 18:56:16</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -999,7 +911,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1009,12 +921,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1024,19 +936,19 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5/22/2026 8:02:19</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1046,7 +958,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1056,7 +968,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1071,19 +983,19 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5/23/2026 14:39:30</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1093,7 +1005,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1108,7 +1020,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1118,19 +1030,19 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5/23/2026 18:20:55</t>
+          <t>2026-05-18 20:08:08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1140,22 +1052,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3,390</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1172,22 +1084,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-14 19:21:49</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1197,10 +1109,20 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1209,35 +1131,45 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-14 19:59:35</t>
+          <t>2026-05-19 11:51:47</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105,386</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1246,12 +1178,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-14 20:34:20</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1261,7 +1193,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1271,24 +1203,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Manual Fix</t>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-14 23:28:39</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1298,7 +1240,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1308,10 +1250,20 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1320,22 +1272,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-16 14:00:21</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1345,19 +1297,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-16 17:39:10</t>
+          <t>5/20/2026 19:07:24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1372,7 +1334,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1382,10 +1344,20 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1394,22 +1366,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-16 18:30:22</t>
+          <t>5/20/2026 19:19:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1419,10 +1391,20 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1431,7 +1413,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-17 09:37:57</t>
+          <t>5/21/2026 18:56:16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1441,12 +1423,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1456,10 +1438,20 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1468,22 +1460,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-17 12:33:11</t>
+          <t>5/22/2026 8:02:19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1493,84 +1485,20 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-05-17 15:41:15</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Cycling</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>4.78</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-05-17 16:46:21</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>7.07</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1619,13 +1547,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59.27</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3390</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -1635,7 +1563,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1651,7 +1579,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.42</v>
+        <v>23.08</v>
       </c>
       <c r="C4" t="n">
         <v>105386</v>
@@ -1689,13 +1617,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63.69</v>
+        <v>104.9</v>
       </c>
       <c r="C6" t="n">
-        <v>108776</v>
+        <v>105386</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,7 +921,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5/20/2026 19:07:24</t>
+          <t>2026-05-20 19:07:24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1366,7 +1366,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5/20/2026 19:19:30</t>
+          <t>2026-05-20 19:19:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1413,7 +1413,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5/21/2026 18:56:16</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1460,7 +1460,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5/22/2026 8:02:19</t>
+          <t>2026-05-22 08:02:19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1499,6 +1499,100 @@
         </is>
       </c>
       <c r="I25" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:39:30</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>5.02</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-23 18:20:55</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>7.44</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3,390</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1547,13 +1641,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77.04000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="C2" t="n">
+        <v>3390</v>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -1585,7 +1679,7 @@
         <v>105386</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1617,13 +1711,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>104.9</v>
+        <v>117.36</v>
       </c>
       <c r="C6" t="n">
-        <v>105386</v>
+        <v>108776</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -1537,7 +1537,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-14 19:21:49</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,16 +482,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>View</t>
@@ -499,19 +507,19 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-14 19:59:35</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -521,16 +529,24 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>View</t>
@@ -545,12 +561,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-14 20:34:20</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -560,16 +576,24 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.07</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>5.77</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>View</t>
@@ -577,19 +601,19 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Manual Fix</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-14 23:28:39</t>
+          <t>2026-05-18 20:08:08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -599,16 +623,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.62</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>View</t>
@@ -623,12 +655,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-16 14:00:21</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -638,16 +670,24 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.46</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>View</t>
@@ -655,38 +695,46 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-16 17:39:10</t>
+          <t>2026-05-19 11:51:47</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>105,386</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>View</t>
@@ -701,7 +749,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-16 18:30:22</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -716,16 +764,24 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.56</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>View</t>
@@ -740,7 +796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-17 09:37:57</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -750,21 +806,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9.29</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>View</t>
@@ -779,31 +843,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-17 12:33:11</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.91</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>6.03</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>View</t>
@@ -818,31 +890,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-17 15:41:15</t>
+          <t>2026-05-20 19:07:24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cycling</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.78</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>View</t>
@@ -857,31 +937,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:21</t>
+          <t>2026-05-20 19:19:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.07</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>View</t>
@@ -896,7 +984,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -911,7 +999,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -926,7 +1014,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -936,19 +1024,19 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-22 08:02:19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -958,7 +1046,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -973,7 +1061,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -990,12 +1078,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-23 14:39:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1005,7 +1093,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1020,7 +1108,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1037,12 +1125,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-18 20:08:08</t>
+          <t>2026-05-23 18:20:55</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1052,12 +1140,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3,390</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1067,7 +1155,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1084,12 +1172,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-25 16:56:39</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1099,12 +1187,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29,156</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1114,7 +1202,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Healthy 365</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1131,27 +1219,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-19 11:51:47</t>
+          <t>2026-05-25 18:37:29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>105,386</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1178,12 +1266,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-25 18:46:04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1193,7 +1281,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1208,7 +1296,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1225,7 +1313,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>5/26/2026 14:21:27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1235,17 +1323,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1,889</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1272,12 +1360,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-05-14 19:21:49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1287,24 +1375,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6.03</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>View</t>
@@ -1319,12 +1399,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-20 19:07:24</t>
+          <t>2026-05-14 19:59:35</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1334,24 +1414,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>View</t>
@@ -1366,39 +1438,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-20 19:19:30</t>
+          <t>2026-05-14 20:34:20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.02</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>View</t>
@@ -1406,19 +1470,19 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Manual Fix</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-14 23:28:39</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1428,24 +1492,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>5.62</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>View</t>
@@ -1460,39 +1516,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-22 08:02:19</t>
+          <t>2026-05-16 14:00:21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.99</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>View</t>
@@ -1500,14 +1548,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-23 14:39:30</t>
+          <t>2026-05-16 17:39:10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1522,24 +1570,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5.02</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>View</t>
@@ -1554,7 +1594,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-05-16 18:30:22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1569,30 +1609,178 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7.44</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>3,390</t>
-        </is>
-      </c>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-17 09:37:57</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>9.29</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-17 12:33:11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>5.91</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-17 15:41:15</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Cycling</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4.78</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-17 16:46:21</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>7.07</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1641,7 +1829,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>89.5</v>
+        <v>102.7</v>
       </c>
       <c r="C2" t="n">
         <v>3390</v>
@@ -1676,7 +1864,7 @@
         <v>23.08</v>
       </c>
       <c r="C4" t="n">
-        <v>105386</v>
+        <v>136431</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1711,10 +1899,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>117.36</v>
+        <v>130.56</v>
       </c>
       <c r="C6" t="n">
-        <v>108776</v>
+        <v>139821</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,27 +467,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-25 16:56:39</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29,156</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Healthy 365</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -507,14 +507,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-25 18:37:29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-25 18:46:04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -608,12 +608,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18 20:08:08</t>
+          <t>2026-05-26 14:21:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -655,22 +655,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-27 09:35:55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -702,27 +702,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-19 11:51:47</t>
+          <t>2026-05-27 18:23:38</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>105,386</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-28 18:44:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,12 +796,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-05-29 17:48:24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Strava App</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -843,12 +843,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-05-29 18:09:22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Garmin Forerunner 265</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-20 19:07:24</t>
+          <t>2026-05-29 19:25:41</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-20 19:19:30</t>
+          <t>2026-05-30 10:55:11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Southwest</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -984,7 +984,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-30 20:44:11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1031,12 +1031,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22 08:02:19</t>
+          <t>2026-05-31 20:24:34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1078,27 +1078,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-23 14:39:30</t>
+          <t>2026-05-31 21:59:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60,056</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1125,27 +1125,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-06-01 09:09:44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3,390</t>
+          <t>44,238</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>fitness app</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1172,12 +1172,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-25 16:56:39</t>
+          <t>5/31/2026 18:29:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>31.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29,156</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Healthy 365</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1212,19 +1212,19 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Committee Approval Required</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-25 18:37:29</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1259,19 +1259,19 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-25 18:46:04</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1313,27 +1313,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5/26/2026 14:21:27</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1,889</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1360,12 +1360,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-14 19:21:49</t>
+          <t>2026-05-18 20:08:08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1375,16 +1375,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>View</t>
@@ -1399,31 +1407,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-14 19:59:35</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>View</t>
@@ -1438,31 +1454,39 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-14 20:34:20</t>
+          <t>2026-05-19 11:51:47</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.07</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>105,386</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>View</t>
@@ -1470,19 +1494,19 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Manual Fix</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-14 23:28:39</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1492,16 +1516,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5.62</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>View</t>
@@ -1516,7 +1548,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-16 14:00:21</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1526,21 +1558,29 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.46</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>View</t>
@@ -1548,19 +1588,19 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-16 17:39:10</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1570,16 +1610,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>6.03</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>View</t>
@@ -1594,12 +1642,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-16 18:30:22</t>
+          <t>2026-05-20 19:07:24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1609,16 +1657,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.56</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>View</t>
@@ -1633,12 +1689,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-17 09:37:57</t>
+          <t>2026-05-20 19:19:30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1648,16 +1704,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9.29</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>View</t>
@@ -1672,31 +1736,39 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-17 12:33:11</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5.91</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>View</t>
@@ -1711,31 +1783,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-17 15:41:15</t>
+          <t>2026-05-22 08:02:19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cycling</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4.78</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>View</t>
@@ -1750,37 +1830,321 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:21</t>
+          <t>2026-05-23 14:39:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>5.02</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-23 18:20:55</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>Jeremy</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>7.07</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>7.44</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3,390</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-01 08:14:08</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>6.31</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Strava App</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>6/1/2026 11:41:23</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>10.44</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Flagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>6/1/2026 14:34:48</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>10.97</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1797,7 +2161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1829,13 +2193,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>102.7</v>
+        <v>168.92</v>
       </c>
       <c r="C2" t="n">
         <v>3390</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1845,7 +2209,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1861,10 +2225,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.08</v>
+        <v>35.42</v>
       </c>
       <c r="C4" t="n">
-        <v>136431</v>
+        <v>238836</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1873,39 +2237,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>130.56</v>
-      </c>
-      <c r="C6" t="n">
-        <v>139821</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
+      <c r="B7" t="n">
+        <v>204.34</v>
+      </c>
+      <c r="C7" t="n">
+        <v>242226</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2145,6 +2145,100 @@
         </is>
       </c>
       <c r="I43" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>6/2/2026 15:45:53</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Surya</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>9,725</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Healthy 365</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>6/2/2026 15:46:13</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Chee</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>29,381</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -2228,7 +2322,7 @@
         <v>35.42</v>
       </c>
       <c r="C4" t="n">
-        <v>238836</v>
+        <v>277942</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2282,7 +2376,7 @@
         <v>204.34</v>
       </c>
       <c r="C7" t="n">
-        <v>242226</v>
+        <v>281332</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,390 +465,102 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-18 18:05:56</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>3.54</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Flagged</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-18 18:45:40</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-18 18:47:54</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kai Fong</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5.77</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-18 20:08:08</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CRX</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>4.14</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-19 06:24:14</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kai Fong</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-19 11:51:47</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Surya</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>105,386</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-05-19 17:28:49</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>3.97</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-05-20 16:07:38</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -858,7 +570,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -873,7 +585,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -883,14 +595,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-20 19:07:24</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -905,7 +617,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -937,22 +649,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-20 19:19:30</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -967,7 +679,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -984,12 +696,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-18 20:08:08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -999,7 +711,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1031,7 +743,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22 08:02:19</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1041,12 +753,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1078,27 +790,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-23 14:39:30</t>
+          <t>2026-05-19 11:51:47</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105,386</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1125,7 +837,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1140,12 +852,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3,390</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1172,27 +884,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-25 16:56:39</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29,156</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1202,7 +914,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Healthy 365</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1219,12 +931,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-25 18:37:29</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1234,7 +946,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1249,7 +961,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1266,12 +978,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-25 18:46:04</t>
+          <t>2026-05-20 19:07:24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1281,7 +993,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1296,7 +1008,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1313,12 +1025,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5/26/2026 14:21:27</t>
+          <t>2026-05-20 19:19:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1328,12 +1040,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1,889</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1343,7 +1055,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1360,7 +1072,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-14 19:21:49</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1375,16 +1087,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>View</t>
@@ -1399,12 +1119,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-14 19:59:35</t>
+          <t>2026-05-22 08:02:19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1414,16 +1134,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>View</t>
@@ -1438,12 +1166,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-14 20:34:20</t>
+          <t>2026-05-23 14:39:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1453,16 +1181,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.07</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>5.02</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>View</t>
@@ -1470,19 +1206,19 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Manual Fix</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-14 23:28:39</t>
+          <t>2026-05-23 18:20:55</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1492,16 +1228,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5.62</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>7.44</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3,390</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>View</t>
@@ -1516,12 +1260,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-16 14:00:21</t>
+          <t>2026-05-25 16:56:39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1531,16 +1275,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.46</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>29,156</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Healthy 365</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>View</t>
@@ -1548,14 +1300,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-16 17:39:10</t>
+          <t>2026-05-25 18:37:29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1570,16 +1322,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>7.57</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>View</t>
@@ -1594,12 +1354,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-16 18:30:22</t>
+          <t>2026-05-25 18:46:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1609,16 +1369,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.56</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>5.63</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>View</t>
@@ -1633,7 +1401,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-17 09:37:57</t>
+          <t>2026-05-26 14:21:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1643,21 +1411,29 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9.29</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>View</t>
@@ -1672,31 +1448,39 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-17 12:33:11</t>
+          <t>2026-05-27 09:35:55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5.91</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>View</t>
@@ -1711,31 +1495,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-17 15:41:15</t>
+          <t>2026-05-27 18:23:38</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cycling</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4.78</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>5.72</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>View</t>
@@ -1750,7 +1542,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:21</t>
+          <t>2026-05-28 18:44:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1765,22 +1557,735 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>7.06</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-29 17:48:24</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>5.93</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Strava App</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-29 18:09:22</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Garmin Forerunner 265</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-29 19:25:41</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>7.25</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-30 10:55:11</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8.16</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Southwest</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-30 20:44:11</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>8.56</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-31 20:24:34</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>7.07</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:59:28</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>60,056</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-01 09:09:44</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>44,238</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>fitness app</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-02 15:45:53</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Surya</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>51,942</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-02 15:46:13</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Chee</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>69,621</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Healthy 365</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-01 08:14:08</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>6.31</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Strava App</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:41:23</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>10.44</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:34:48</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>10.97</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-02 19:19:37</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>7.23</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-02 20:32:59</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1797,7 +2302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1829,7 +2334,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>102.7</v>
+        <v>179.67</v>
       </c>
       <c r="C2" t="n">
         <v>3390</v>
@@ -1845,7 +2350,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1861,10 +2366,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.08</v>
+        <v>4.42</v>
       </c>
       <c r="C4" t="n">
-        <v>136431</v>
+        <v>360399</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1873,38 +2378,54 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>130.56</v>
-      </c>
-      <c r="C6" t="n">
-        <v>139821</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="B7" t="n">
+        <v>184.09</v>
+      </c>
+      <c r="C7" t="n">
+        <v>363789</v>
+      </c>
+      <c r="D7" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2286,6 +2286,147 @@
         </is>
       </c>
       <c r="I46" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>6/3/2026 18:46:11</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>5.77</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>6/3/2026 18:54:32</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>7.24</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Flagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>6/3/2026 18:59:20</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -2334,13 +2475,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>179.67</v>
+        <v>202.74</v>
       </c>
       <c r="C2" t="n">
         <v>3390</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -2420,13 +2561,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>184.09</v>
+        <v>207.16</v>
       </c>
       <c r="C7" t="n">
         <v>363789</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,102 +465,390 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-25 16:56:39</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>29,156</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Healthy 365</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-25 18:37:29</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7.57</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-25 18:46:04</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5.63</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:21:27</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:35:55</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:23:38</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5.72</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-28 18:44:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7.06</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-29 17:48:24</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5.93</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Strava App</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-29 18:09:22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -570,7 +858,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -585,7 +873,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin Forerunner 265</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -595,19 +883,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-29 19:25:41</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -617,7 +905,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -632,7 +920,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -649,12 +937,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-30 10:55:11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -664,7 +952,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -679,7 +967,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Southwest</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -696,12 +984,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18 20:08:08</t>
+          <t>2026-05-30 20:44:11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -711,7 +999,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -726,7 +1014,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -743,22 +1031,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-31 20:24:34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -773,7 +1061,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -790,12 +1078,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-19 11:51:47</t>
+          <t>2026-05-31 21:59:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -810,7 +1098,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>105,386</t>
+          <t>60,056</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -820,7 +1108,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -837,27 +1125,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-06-01 09:09:44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44,238</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -867,7 +1155,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>fitness app</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -884,27 +1172,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-06-02 15:45:53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51,942</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -931,27 +1219,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-06-02 15:46:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Chee</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69,621</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -961,7 +1249,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Healthy 365</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -978,12 +1266,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-20 19:07:24</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -993,7 +1281,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1008,7 +1296,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1018,14 +1306,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-20 19:19:30</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1035,12 +1323,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1072,12 +1360,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1087,7 +1375,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1119,12 +1407,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22 08:02:19</t>
+          <t>2026-05-18 20:08:08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1134,7 +1422,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1166,22 +1454,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-23 14:39:30</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1196,7 +1484,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1213,27 +1501,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-05-19 11:51:47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3,390</t>
+          <t>105,386</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1243,7 +1531,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1260,27 +1548,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-25 16:56:39</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>29,156</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1290,7 +1578,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Healthy 365</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1307,12 +1595,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-25 18:37:29</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1322,7 +1610,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1337,7 +1625,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1354,7 +1642,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-25 18:46:04</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1369,7 +1657,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1401,12 +1689,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-26 14:21:27</t>
+          <t>2026-05-20 19:07:24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1416,7 +1704,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1431,7 +1719,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1448,7 +1736,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-27 09:35:55</t>
+          <t>2026-05-20 19:19:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1458,12 +1746,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1495,12 +1783,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-27 18:23:38</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1510,7 +1798,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1542,12 +1830,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-28 18:44:00</t>
+          <t>2026-05-22 08:02:19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1557,7 +1845,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1572,7 +1860,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1589,12 +1877,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-29 17:48:24</t>
+          <t>2026-05-23 14:39:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1604,7 +1892,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1619,7 +1907,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Strava App</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1636,12 +1924,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-29 18:09:22</t>
+          <t>2026-05-23 18:20:55</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1651,12 +1939,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3,390</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1666,7 +1954,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Garmin Forerunner 265</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1681,380 +1969,92 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-05-29 19:25:41</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>7.25</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-05-30 10:55:11</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>8.16</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Southwest</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-05-30 20:44:11</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>8.56</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-05-31 20:24:34</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>7.07</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-05-31 21:59:28</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Ron</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>60,056</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-06-01 09:09:44</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>CRX</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>44,238</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>fitness app</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-06-02 15:45:53</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Surya</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>51,942</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-06-02 15:46:13</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Chee</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>69,621</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Healthy 365</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2427,6 +2427,194 @@
         </is>
       </c>
       <c r="I49" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>6/4/2026 19:03:19</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>7.11</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>6/5/2026 15:56:04</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Chun Chieh</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>5.92</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>[View](https://drive.google.com/open?id=1Q9zUXLONTYDHfMtPO0rU9Pv6q9SQgzHN, https://drive.google.com/open?id=10L433gnJQHuEM7vGBbgb8gQpXSKHwotf, https://drive.google.com/open?id=16ucwKYvjDUAEkqXTJCHpZF44eb6sfeII)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>6/5/2026 18:50:18</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>7.30</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>6/5/2026 18:50:59</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>5.58</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -2475,13 +2663,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>202.74</v>
+        <v>228.65</v>
       </c>
       <c r="C2" t="n">
         <v>3390</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2561,13 +2749,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>207.16</v>
+        <v>233.07</v>
       </c>
       <c r="C7" t="n">
         <v>363789</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,390 +465,102 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-25 16:56:39</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CRX</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>29,156</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Healthy 365</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-25 18:37:29</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>7.57</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-25 18:46:04</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kai Fong</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5.63</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-26 14:21:27</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-27 09:35:55</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>7.56</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-27 18:23:38</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kai Fong</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>5.72</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-05-28 18:44:00</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>7.06</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-05-29 17:48:24</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Kai Fong</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>5.93</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Strava App</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-29 18:09:22</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -858,7 +570,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -873,7 +585,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Garmin Forerunner 265</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -883,19 +595,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:41</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -905,7 +617,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -920,7 +632,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -937,12 +649,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-30 10:55:11</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -952,7 +664,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -967,7 +679,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Southwest</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -984,12 +696,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-30 20:44:11</t>
+          <t>2026-05-18 20:08:08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -999,7 +711,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1014,7 +726,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1031,22 +743,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-31 20:24:34</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1061,7 +773,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1078,12 +790,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-31 21:59:28</t>
+          <t>2026-05-19 11:51:47</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1098,7 +810,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>60,056</t>
+          <t>105,386</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1108,7 +820,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1125,27 +837,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-01 09:09:44</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>44,238</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1155,7 +867,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>fitness app</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1172,27 +884,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-02 15:45:53</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>51,942</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1219,27 +931,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-02 15:46:13</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chee</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>69,621</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1249,7 +961,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Healthy 365</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1266,12 +978,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-20 19:07:24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1281,7 +993,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1296,7 +1008,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1306,14 +1018,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-20 19:19:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1323,12 +1035,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1360,12 +1072,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1375,7 +1087,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1407,12 +1119,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-18 20:08:08</t>
+          <t>2026-05-22 08:02:19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1422,7 +1134,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1454,22 +1166,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-23 14:39:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1484,7 +1196,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1501,27 +1213,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-19 11:51:47</t>
+          <t>2026-05-23 18:20:55</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>105,386</t>
+          <t>3,390</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1531,7 +1243,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1548,27 +1260,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-25 16:56:39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29,156</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1578,7 +1290,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Healthy 365</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1595,12 +1307,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-05-25 18:37:29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1610,7 +1322,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1625,7 +1337,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1642,7 +1354,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-05-25 18:46:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1657,7 +1369,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1689,12 +1401,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-20 19:07:24</t>
+          <t>2026-05-26 14:21:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1704,7 +1416,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1719,7 +1431,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1736,7 +1448,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-20 19:19:30</t>
+          <t>2026-05-27 09:35:55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1746,12 +1458,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1783,12 +1495,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-27 18:23:38</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1798,7 +1510,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1830,12 +1542,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22 08:02:19</t>
+          <t>2026-05-28 18:44:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1845,7 +1557,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1860,7 +1572,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1877,12 +1589,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-23 14:39:30</t>
+          <t>2026-05-29 17:48:24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1892,7 +1604,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1907,7 +1619,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Strava App</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1924,137 +1636,425 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-05-29 18:09:22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Garmin Forerunner 265</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-29 19:25:41</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>Jeremy</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>7.44</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>3,390</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>7.25</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-30 10:55:11</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8.16</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Southwest</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-30 20:44:11</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>8.56</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-31 20:24:34</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>7.07</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:59:28</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>60,056</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-01 09:09:44</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>44,238</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>fitness app</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-02 15:45:53</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Surya</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>51,942</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>Google Fit</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-02 15:46:13</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Chee</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>69,621</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Healthy 365</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,102 +465,390 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-25 16:56:39</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>29,156</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Healthy 365</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-25 18:37:29</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7.57</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-25 18:46:04</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5.63</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:21:27</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:35:55</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:23:38</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5.72</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-28 18:44:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7.06</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-29 17:48:24</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5.93</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Strava App</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-29 18:09:22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -570,7 +858,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -585,7 +873,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin Forerunner 265</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -595,19 +883,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-29 19:25:41</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -617,7 +905,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -632,7 +920,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -649,12 +937,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-30 10:55:11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -664,7 +952,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -679,7 +967,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Southwest</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -696,12 +984,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18 20:08:08</t>
+          <t>2026-05-30 20:44:11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -711,7 +999,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -726,7 +1014,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -743,22 +1031,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-31 20:24:34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -773,7 +1061,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -790,12 +1078,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-19 11:51:47</t>
+          <t>2026-05-31 21:59:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -810,7 +1098,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>105,386</t>
+          <t>60,056</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -820,7 +1108,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -837,27 +1125,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-06-01 09:09:44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44,238</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -867,7 +1155,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>fitness app</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -884,27 +1172,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-06-02 15:45:53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51,942</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -931,27 +1219,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-06-02 15:46:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Chee</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69,621</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -961,7 +1249,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Healthy 365</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -978,12 +1266,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-20 19:07:24</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -993,7 +1281,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1008,7 +1296,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1018,14 +1306,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-20 19:19:30</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1035,12 +1323,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1072,12 +1360,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1087,7 +1375,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1119,12 +1407,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22 08:02:19</t>
+          <t>2026-05-18 20:08:08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1134,7 +1422,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1166,22 +1454,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-23 14:39:30</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1196,7 +1484,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1213,27 +1501,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-05-19 11:51:47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3,390</t>
+          <t>105,386</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1243,7 +1531,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1260,27 +1548,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-25 16:56:39</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>29,156</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1290,7 +1578,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Healthy 365</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1307,12 +1595,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-25 18:37:29</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1322,7 +1610,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1337,7 +1625,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1354,7 +1642,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-25 18:46:04</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1369,7 +1657,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1401,12 +1689,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-26 14:21:27</t>
+          <t>2026-05-20 19:07:24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1416,7 +1704,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1431,7 +1719,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1448,7 +1736,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-27 09:35:55</t>
+          <t>2026-05-20 19:19:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1458,12 +1746,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1495,12 +1783,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-27 18:23:38</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1510,7 +1798,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1542,12 +1830,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-28 18:44:00</t>
+          <t>2026-05-22 08:02:19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1557,7 +1845,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1572,7 +1860,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1589,12 +1877,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-29 17:48:24</t>
+          <t>2026-05-23 14:39:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1604,7 +1892,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1619,7 +1907,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Strava App</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1636,12 +1924,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-29 18:09:22</t>
+          <t>2026-05-23 18:20:55</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1651,12 +1939,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3,390</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1666,7 +1954,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Garmin Forerunner 265</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1681,380 +1969,92 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-05-29 19:25:41</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>7.25</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-05-30 10:55:11</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>8.16</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Southwest</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-05-30 20:44:11</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>8.56</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-05-31 20:24:34</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>7.07</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-05-31 21:59:28</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Ron</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>60,056</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-06-01 09:09:44</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>CRX</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>44,238</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>fitness app</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-06-02 15:45:53</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Surya</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>51,942</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-06-02 15:46:13</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Chee</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>69,621</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Healthy 365</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2617,6 +2617,53 @@
       <c r="I53" t="inlineStr">
         <is>
           <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>6/6/2026 8:36:45</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>10.25</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
         </is>
       </c>
     </row>
@@ -2663,13 +2710,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>228.65</v>
+        <v>238.9</v>
       </c>
       <c r="C2" t="n">
         <v>3390</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2749,13 +2796,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>233.07</v>
+        <v>243.32</v>
       </c>
       <c r="C7" t="n">
         <v>363789</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2623,45 +2623,139 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>6/6/2026 18:18:05</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>6/6/2026 8:36:45</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Kelvin</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>10.25</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>6/7/2026 12:17:03</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>10.35</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
         <is>
           <t>Committee Approval Required</t>
         </is>
@@ -2710,13 +2804,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>238.9</v>
+        <v>249.25</v>
       </c>
       <c r="C2" t="n">
         <v>3390</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -2796,13 +2890,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>243.32</v>
+        <v>253.67</v>
       </c>
       <c r="C7" t="n">
         <v>363789</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,390 +465,102 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-25 16:56:39</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CRX</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>29,156</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Healthy 365</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-25 18:37:29</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>7.57</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-25 18:46:04</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kai Fong</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5.63</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-26 14:21:27</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-27 09:35:55</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>7.56</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-27 18:23:38</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kai Fong</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>5.72</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-05-28 18:44:00</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>7.06</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-05-29 17:48:24</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Kai Fong</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>5.93</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Strava App</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-29 18:09:22</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -858,7 +570,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -873,7 +585,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Garmin Forerunner 265</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -883,19 +595,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:41</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -905,7 +617,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -920,7 +632,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -937,12 +649,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-30 10:55:11</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -952,7 +664,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -967,7 +679,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Southwest</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -984,12 +696,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-30 20:44:11</t>
+          <t>2026-05-18 20:08:08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -999,7 +711,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1014,7 +726,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1031,22 +743,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-31 20:24:34</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1061,7 +773,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1078,12 +790,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-31 21:59:28</t>
+          <t>2026-05-19 11:51:47</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1098,7 +810,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>60,056</t>
+          <t>105,386</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1108,7 +820,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1125,27 +837,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-01 09:09:44</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>44,238</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1155,7 +867,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>fitness app</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1172,27 +884,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-02 15:45:53</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>51,942</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1219,27 +931,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-02 15:46:13</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chee</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>69,621</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1249,7 +961,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Healthy 365</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1266,12 +978,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-20 19:07:24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1281,7 +993,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1296,7 +1008,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1306,14 +1018,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-20 19:19:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1323,12 +1035,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1360,12 +1072,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1375,7 +1087,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1407,12 +1119,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-18 20:08:08</t>
+          <t>2026-05-22 08:02:19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1422,7 +1134,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1454,22 +1166,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-23 14:39:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1484,7 +1196,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1501,27 +1213,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-19 11:51:47</t>
+          <t>2026-05-23 18:20:55</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>105,386</t>
+          <t>3,390</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1531,7 +1243,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1548,27 +1260,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-25 16:56:39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29,156</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1578,7 +1290,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Healthy 365</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1595,12 +1307,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-05-25 18:37:29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1610,7 +1322,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1625,7 +1337,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1642,7 +1354,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-05-25 18:46:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1657,7 +1369,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1689,12 +1401,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-20 19:07:24</t>
+          <t>2026-05-26 14:21:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1704,7 +1416,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1719,7 +1431,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1736,7 +1448,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-20 19:19:30</t>
+          <t>2026-05-27 09:35:55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1746,12 +1458,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1783,12 +1495,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-27 18:23:38</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1798,7 +1510,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1830,12 +1542,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22 08:02:19</t>
+          <t>2026-05-28 18:44:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1845,7 +1557,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1860,7 +1572,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1877,12 +1589,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-23 14:39:30</t>
+          <t>2026-05-29 17:48:24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1892,7 +1604,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1907,7 +1619,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Strava App</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1924,137 +1636,425 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-05-29 18:09:22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Garmin Forerunner 265</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-29 19:25:41</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>Jeremy</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>7.44</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>3,390</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>7.25</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-30 10:55:11</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8.16</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Southwest</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-30 20:44:11</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>8.56</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-31 20:24:34</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>7.07</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:59:28</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>60,056</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-01 09:09:44</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>44,238</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>fitness app</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-02 15:45:53</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Surya</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>51,942</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>Google Fit</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-02 15:46:13</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Chee</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>69,621</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Healthy 365</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>249.25</v>
+        <v>256.71</v>
       </c>
       <c r="C2" t="n">
         <v>3390</v>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253.67</v>
+        <v>261.13</v>
       </c>
       <c r="C7" t="n">
         <v>363789</v>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -2267,7 +2267,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3,012</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2807,7 +2807,7 @@
         <v>256.71</v>
       </c>
       <c r="C2" t="n">
-        <v>3390</v>
+        <v>6402</v>
       </c>
       <c r="D2" t="n">
         <v>18</v>
@@ -2893,7 +2893,7 @@
         <v>261.13</v>
       </c>
       <c r="C7" t="n">
-        <v>363789</v>
+        <v>366801</v>
       </c>
       <c r="D7" t="n">
         <v>18</v>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2756,6 +2756,100 @@
         </is>
       </c>
       <c r="I56" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>6/7/2026 17:27:12</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Chun Chieh</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>16.44</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>25,078</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>6/7/2026 18:45:45</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -2804,10 +2898,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>256.71</v>
+        <v>280.53</v>
       </c>
       <c r="C2" t="n">
-        <v>6402</v>
+        <v>31480</v>
       </c>
       <c r="D2" t="n">
         <v>18</v>
@@ -2890,10 +2984,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>261.13</v>
+        <v>284.95</v>
       </c>
       <c r="C7" t="n">
-        <v>366801</v>
+        <v>391879</v>
       </c>
       <c r="D7" t="n">
         <v>18</v>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2850,6 +2850,194 @@
         </is>
       </c>
       <c r="I58" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>6/7/2026 19:14:51</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>5.51</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>4,532</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>6/7/2026 19:14:51</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>5,470</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>6/7/2026 19:14:51</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>3,398</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>6/7/2026 19:14:51</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>6,624</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -2898,10 +3086,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>280.53</v>
+        <v>299.22</v>
       </c>
       <c r="C2" t="n">
-        <v>31480</v>
+        <v>51504</v>
       </c>
       <c r="D2" t="n">
         <v>18</v>
@@ -2984,10 +3172,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>284.95</v>
+        <v>303.64</v>
       </c>
       <c r="C7" t="n">
-        <v>391879</v>
+        <v>411903</v>
       </c>
       <c r="D7" t="n">
         <v>18</v>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3038,6 +3038,53 @@
         </is>
       </c>
       <c r="I62" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>6/7/2026 21:02:41</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Chee</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>52,564</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Healthy 365</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -3121,7 +3168,7 @@
         <v>4.42</v>
       </c>
       <c r="C4" t="n">
-        <v>360399</v>
+        <v>412963</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -3175,7 +3222,7 @@
         <v>303.64</v>
       </c>
       <c r="C7" t="n">
-        <v>411903</v>
+        <v>464467</v>
       </c>
       <c r="D7" t="n">
         <v>18</v>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2106,27 +2106,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01 11:41:23</t>
+          <t>2026-06-01 09:09:44</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44,238</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Healthy 365</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2153,12 +2153,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-01 14:34:48</t>
+          <t>2026-06-01 11:41:23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2200,7 +2200,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-02 19:19:37</t>
+          <t>2026-06-01 14:34:48</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2247,12 +2247,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-02 20:32:59</t>
+          <t>2026-06-02 19:19:37</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3,012</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2294,12 +2294,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6/3/2026 18:46:11</t>
+          <t>2026-06-02 20:32:59</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2309,17 +2309,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3,012</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2341,12 +2341,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6/3/2026 18:54:32</t>
+          <t>6/3/2026 18:46:11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2381,19 +2381,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6/3/2026 18:59:20</t>
+          <t>6/3/2026 18:54:32</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2428,19 +2428,19 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6/4/2026 19:03:19</t>
+          <t>6/3/2026 18:59:20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2482,12 +2482,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6/5/2026 15:56:04</t>
+          <t>6/4/2026 19:03:19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Chun Chieh</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[View](https://drive.google.com/open?id=1Q9zUXLONTYDHfMtPO0rU9Pv6q9SQgzHN, https://drive.google.com/open?id=10L433gnJQHuEM7vGBbgb8gQpXSKHwotf, https://drive.google.com/open?id=16ucwKYvjDUAEkqXTJCHpZF44eb6sfeII)</t>
+          <t>View</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2529,12 +2529,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6/5/2026 18:50:18</t>
+          <t>6/5/2026 15:56:04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Chun Chieh</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>[View](https://drive.google.com/open?id=1Q9zUXLONTYDHfMtPO0rU9Pv6q9SQgzHN, https://drive.google.com/open?id=10L433gnJQHuEM7vGBbgb8gQpXSKHwotf, https://drive.google.com/open?id=16ucwKYvjDUAEkqXTJCHpZF44eb6sfeII)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2576,12 +2576,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6/5/2026 18:50:59</t>
+          <t>6/5/2026 18:50:18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6/6/2026 18:18:05</t>
+          <t>6/5/2026 18:50:59</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2670,12 +2670,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6/6/2026 8:36:45</t>
+          <t>6/6/2026 18:18:05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2717,7 +2717,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6/7/2026 12:17:03</t>
+          <t>6/6/2026 8:36:45</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2764,12 +2764,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6/7/2026 17:27:12</t>
+          <t>6/7/2026 12:17:03</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Chun Chieh</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2779,17 +2779,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>25,078</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2811,12 +2811,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6/7/2026 18:45:45</t>
+          <t>6/7/2026 17:27:12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Chun Chieh</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25,078</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2858,12 +2858,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6/7/2026 19:14:51</t>
+          <t>6/7/2026 18:45:45</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4,532</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>5,470</t>
+          <t>4,532</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>3,398</t>
+          <t>5,470</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>6,624</t>
+          <t>3,398</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3046,45 +3046,139 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>6/7/2026 19:14:51</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>6,624</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>6/7/2026 21:02:41</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Chee</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>52,564</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>Healthy 365</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>6/8/2026 06:03:23</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>99,091</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Healthy 365</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -3168,7 +3262,7 @@
         <v>4.42</v>
       </c>
       <c r="C4" t="n">
-        <v>412963</v>
+        <v>556292</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -3222,7 +3316,7 @@
         <v>303.64</v>
       </c>
       <c r="C7" t="n">
-        <v>464467</v>
+        <v>607796</v>
       </c>
       <c r="D7" t="n">
         <v>18</v>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,102 +465,390 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-25 16:56:39</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>29,156</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Healthy 365</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-25 18:37:29</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7.57</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-25 18:46:04</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5.63</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:21:27</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:35:55</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:23:38</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5.72</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-28 18:44:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7.06</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-29 17:48:24</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5.93</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Strava App</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-29 18:09:22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -570,7 +858,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -585,7 +873,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin Forerunner 265</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -595,19 +883,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-29 19:25:41</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -617,7 +905,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -632,7 +920,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -649,12 +937,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-30 10:55:11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -664,7 +952,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -679,7 +967,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Southwest</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -696,12 +984,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18 20:08:08</t>
+          <t>2026-05-30 20:44:11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -711,7 +999,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -726,7 +1014,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -743,22 +1031,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-31 20:24:34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -773,7 +1061,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -790,12 +1078,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-19 11:51:47</t>
+          <t>2026-05-31 21:59:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -810,7 +1098,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>105,386</t>
+          <t>60,056</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -820,7 +1108,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -837,27 +1125,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-06-01 09:09:44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44,238</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -867,7 +1155,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>fitness app</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -884,27 +1172,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-06-02 15:45:53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51,942</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -931,27 +1219,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-06-02 15:46:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Chee</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69,621</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -961,7 +1249,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Healthy 365</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -978,12 +1266,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-20 19:07:24</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -993,7 +1281,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1008,7 +1296,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1018,14 +1306,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-20 19:19:30</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1035,12 +1323,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1072,12 +1360,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1087,7 +1375,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1119,12 +1407,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22 08:02:19</t>
+          <t>2026-05-18 20:08:08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1134,7 +1422,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1166,22 +1454,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-23 14:39:30</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1196,7 +1484,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1213,27 +1501,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-05-19 11:51:47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3,390</t>
+          <t>105,386</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1243,7 +1531,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1260,27 +1548,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-25 16:56:39</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>29,156</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1290,7 +1578,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Healthy 365</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1307,12 +1595,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-25 18:37:29</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1322,7 +1610,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1337,7 +1625,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1354,7 +1642,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-25 18:46:04</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1369,7 +1657,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1401,12 +1689,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-26 14:21:27</t>
+          <t>2026-05-20 19:07:24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1416,7 +1704,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1431,7 +1719,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1448,7 +1736,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-27 09:35:55</t>
+          <t>2026-05-20 19:19:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1458,12 +1746,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1495,12 +1783,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-27 18:23:38</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1510,7 +1798,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1542,12 +1830,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-28 18:44:00</t>
+          <t>2026-05-22 08:02:19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1557,7 +1845,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1572,7 +1860,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1589,12 +1877,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-29 17:48:24</t>
+          <t>2026-05-23 14:39:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1604,7 +1892,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1619,7 +1907,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Strava App</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1636,12 +1924,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-29 18:09:22</t>
+          <t>2026-05-23 18:20:55</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1651,12 +1939,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3,390</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1666,7 +1954,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Garmin Forerunner 265</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1681,380 +1969,92 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-05-29 19:25:41</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>7.25</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-05-30 10:55:11</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>8.16</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Southwest</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-05-30 20:44:11</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>8.56</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-05-31 20:24:34</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>7.07</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-05-31 21:59:28</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Ron</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>60,056</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-06-01 09:09:44</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>CRX</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>44,238</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>fitness app</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-06-02 15:45:53</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Surya</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>51,942</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-06-02 15:46:13</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Chee</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>69,621</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Healthy 365</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3181,6 +3181,194 @@
       <c r="I65" t="inlineStr">
         <is>
           <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>6/8/2026 11:26:59</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Surya</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>4,204</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>6/8/2026 6:03:23</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>6/8/2026 8:21:19</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Chun Chieh</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>11.35</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>6/8/2026 9:39:05</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
         </is>
       </c>
     </row>
@@ -3259,10 +3447,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.42</v>
+        <v>15.77</v>
       </c>
       <c r="C4" t="n">
-        <v>556292</v>
+        <v>560496</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -3313,10 +3501,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>303.64</v>
+        <v>314.99</v>
       </c>
       <c r="C7" t="n">
-        <v>607796</v>
+        <v>612000</v>
       </c>
       <c r="D7" t="n">
         <v>18</v>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3369,6 +3369,100 @@
       <c r="I69" t="inlineStr">
         <is>
           <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>6/9/2026 6:28:24</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>6/9/2026 9:34:20</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>10.30</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
@@ -3415,13 +3509,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>299.22</v>
+        <v>309.52</v>
       </c>
       <c r="C2" t="n">
         <v>51504</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -3501,13 +3595,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>314.99</v>
+        <v>325.29</v>
       </c>
       <c r="C7" t="n">
         <v>612000</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3375,22 +3375,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6/9/2026 6:28:24</t>
+          <t>6/9/2026 18:31:22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3422,45 +3422,92 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>6/9/2026 6:28:24</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>6/9/2026 9:34:20</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>Kelvin</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
         <is>
           <t>10.30</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Garmin</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
         <is>
           <t>Flagged</t>
         </is>
@@ -3509,13 +3556,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>309.52</v>
+        <v>316.57</v>
       </c>
       <c r="C2" t="n">
         <v>51504</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -3595,13 +3642,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>325.29</v>
+        <v>332.34</v>
       </c>
       <c r="C7" t="n">
         <v>612000</v>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,390 +465,102 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-25 16:56:39</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CRX</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>29,156</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Healthy 365</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-25 18:37:29</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>7.57</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-25 18:46:04</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kai Fong</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5.63</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-26 14:21:27</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-27 09:35:55</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>7.56</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-27 18:23:38</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kai Fong</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>5.72</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-05-28 18:44:00</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>7.06</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-05-29 17:48:24</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Kai Fong</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>5.93</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Strava App</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-29 18:09:22</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -858,7 +570,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -873,7 +585,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Garmin Forerunner 265</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -883,19 +595,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:41</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -905,7 +617,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -920,7 +632,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -937,12 +649,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-30 10:55:11</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -952,7 +664,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -967,7 +679,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Southwest</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -984,12 +696,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-30 20:44:11</t>
+          <t>2026-05-18 20:08:08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -999,7 +711,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1014,7 +726,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1031,22 +743,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-31 20:24:34</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1061,7 +773,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1078,12 +790,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-31 21:59:28</t>
+          <t>2026-05-19 11:51:47</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1098,7 +810,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>60,056</t>
+          <t>105,386</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1108,7 +820,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1125,27 +837,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-01 09:09:44</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>44,238</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1155,7 +867,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>fitness app</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1172,27 +884,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-02 15:45:53</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>51,942</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1219,27 +931,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-02 15:46:13</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chee</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>69,621</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1249,7 +961,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Healthy 365</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1266,12 +978,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-20 19:07:24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1281,7 +993,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1296,7 +1008,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1306,14 +1018,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-20 19:19:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1323,12 +1035,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1360,12 +1072,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1375,7 +1087,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1407,12 +1119,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-18 20:08:08</t>
+          <t>2026-05-22 08:02:19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1422,7 +1134,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1454,22 +1166,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-23 14:39:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1484,7 +1196,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1501,27 +1213,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-19 11:51:47</t>
+          <t>2026-05-23 18:20:55</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>105,386</t>
+          <t>3,390</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1531,7 +1243,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1548,27 +1260,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-25 16:56:39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29,156</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1578,7 +1290,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Healthy 365</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1595,12 +1307,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-05-25 18:37:29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1610,7 +1322,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1625,7 +1337,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1642,7 +1354,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-05-25 18:46:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1657,7 +1369,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1689,12 +1401,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-20 19:07:24</t>
+          <t>2026-05-26 14:21:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1704,7 +1416,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1719,7 +1431,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1736,7 +1448,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-20 19:19:30</t>
+          <t>2026-05-27 09:35:55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1746,12 +1458,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1783,12 +1495,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-27 18:23:38</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1798,7 +1510,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1830,12 +1542,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22 08:02:19</t>
+          <t>2026-05-28 18:44:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1845,7 +1557,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1860,7 +1572,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1877,12 +1589,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-23 14:39:30</t>
+          <t>2026-05-29 17:48:24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1892,7 +1604,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1907,7 +1619,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Strava App</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1924,137 +1636,425 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-05-29 18:09:22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Garmin Forerunner 265</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-29 19:25:41</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>Jeremy</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>7.44</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>3,390</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>7.25</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-30 10:55:11</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8.16</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Southwest</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-30 20:44:11</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>8.56</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-31 20:24:34</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>7.07</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:59:28</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>60,056</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-01 09:09:44</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>44,238</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>fitness app</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-02 15:45:53</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Surya</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>51,942</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>Google Fit</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-02 15:46:13</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Chee</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>69,621</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Healthy 365</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2106,27 +2106,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01 09:09:44</t>
+          <t>2026-06-01 11:41:23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>44,238</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Healthy 365</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2153,12 +2153,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-01 11:41:23</t>
+          <t>2026-06-01 14:34:48</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2200,7 +2200,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-01 14:34:48</t>
+          <t>2026-06-02 19:19:37</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2247,12 +2247,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-02 19:19:37</t>
+          <t>2026-06-02 20:32:59</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3,012</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2294,12 +2294,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-02 20:32:59</t>
+          <t>6/3/2026 18:46:11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2309,17 +2309,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3,012</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2341,12 +2341,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6/3/2026 18:46:11</t>
+          <t>6/3/2026 18:54:32</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2381,19 +2381,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6/3/2026 18:54:32</t>
+          <t>6/3/2026 18:59:20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2428,19 +2428,19 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6/3/2026 18:59:20</t>
+          <t>6/4/2026 19:03:19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2482,12 +2482,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6/4/2026 19:03:19</t>
+          <t>6/5/2026 15:56:04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Chun Chieh</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>[View](https://drive.google.com/open?id=1Q9zUXLONTYDHfMtPO0rU9Pv6q9SQgzHN, https://drive.google.com/open?id=10L433gnJQHuEM7vGBbgb8gQpXSKHwotf, https://drive.google.com/open?id=16ucwKYvjDUAEkqXTJCHpZF44eb6sfeII)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2529,12 +2529,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6/5/2026 15:56:04</t>
+          <t>6/5/2026 18:50:18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chun Chieh</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[View](https://drive.google.com/open?id=1Q9zUXLONTYDHfMtPO0rU9Pv6q9SQgzHN, https://drive.google.com/open?id=10L433gnJQHuEM7vGBbgb8gQpXSKHwotf, https://drive.google.com/open?id=16ucwKYvjDUAEkqXTJCHpZF44eb6sfeII)</t>
+          <t>View</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2576,12 +2576,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6/5/2026 18:50:18</t>
+          <t>6/5/2026 18:50:59</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6/5/2026 18:50:59</t>
+          <t>6/6/2026 18:18:05</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2670,12 +2670,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6/6/2026 18:18:05</t>
+          <t>6/6/2026 8:36:45</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2717,7 +2717,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6/6/2026 8:36:45</t>
+          <t>6/7/2026 12:17:03</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2764,12 +2764,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6/7/2026 12:17:03</t>
+          <t>6/7/2026 17:27:12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Chun Chieh</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2779,17 +2779,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25,078</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2811,12 +2811,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6/7/2026 17:27:12</t>
+          <t>6/7/2026 18:45:45</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Chun Chieh</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>25,078</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2858,12 +2858,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6/7/2026 18:45:45</t>
+          <t>6/7/2026 19:14:51</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4,532</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>4,532</t>
+          <t>5,470</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>5,470</t>
+          <t>3,398</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>3,398</t>
+          <t>6,624</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3046,27 +3046,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6/7/2026 19:14:51</t>
+          <t>6/7/2026 21:02:41</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Chee</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>6,624</t>
+          <t>52,564</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Healthy 365</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3093,12 +3093,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6/7/2026 21:02:41</t>
+          <t>6/8/2026 06:03:23</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Chee</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>52,564</t>
+          <t>99,091</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3140,12 +3140,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6/8/2026 06:03:23</t>
+          <t>6/8/2026 11:26:59</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>99,091</t>
+          <t>4,204</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Healthy 365</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3180,19 +3180,19 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Committee Approval Required</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6/8/2026 11:26:59</t>
+          <t>6/8/2026 6:03:23</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>4,204</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3234,12 +3234,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6/8/2026 6:03:23</t>
+          <t>6/8/2026 8:21:19</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Chun Chieh</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3281,12 +3281,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6/8/2026 8:21:19</t>
+          <t>6/8/2026 9:39:05</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chun Chieh</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3328,22 +3328,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6/8/2026 9:39:05</t>
+          <t>6/9/2026 18:31:22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3375,22 +3375,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6/9/2026 18:31:22</t>
+          <t>6/9/2026 6:28:24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3422,22 +3422,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6/9/2026 6:28:24</t>
+          <t>6/9/2026 9:34:20</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3447,12 +3447,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3461,53 +3461,6 @@
         </is>
       </c>
       <c r="I71" t="inlineStr">
-        <is>
-          <t>Committee Approval Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>6/9/2026 9:34:20</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>10.30</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
         <is>
           <t>Flagged</t>
         </is>
@@ -3591,7 +3544,7 @@
         <v>15.77</v>
       </c>
       <c r="C4" t="n">
-        <v>560496</v>
+        <v>516258</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -3645,7 +3598,7 @@
         <v>332.34</v>
       </c>
       <c r="C7" t="n">
-        <v>612000</v>
+        <v>567762</v>
       </c>
       <c r="D7" t="n">
         <v>23</v>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3140,27 +3140,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6/8/2026 11:26:59</t>
+          <t>6/8/2026 8:21:19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Chun Chieh</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>4,204</t>
+          <t>17,132</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3180,19 +3180,19 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6/8/2026 6:03:23</t>
+          <t>6/8/2026 11:26:59</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4,204</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3234,12 +3234,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6/8/2026 8:21:19</t>
+          <t>6/9/2026 6:28:24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Chun Chieh</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3281,22 +3281,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6/8/2026 9:39:05</t>
+          <t>6/9/2026 9:34:20</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
@@ -3369,100 +3369,6 @@
       <c r="I69" t="inlineStr">
         <is>
           <t>Committee Approval Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>6/9/2026 6:28:24</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Ron</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Committee Approval Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>6/9/2026 9:34:20</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>10.30</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Flagged</t>
         </is>
       </c>
     </row>
@@ -3509,10 +3415,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>316.57</v>
+        <v>327.92</v>
       </c>
       <c r="C2" t="n">
-        <v>51504</v>
+        <v>68636</v>
       </c>
       <c r="D2" t="n">
         <v>23</v>
@@ -3541,7 +3447,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.77</v>
+        <v>4.42</v>
       </c>
       <c r="C4" t="n">
         <v>516258</v>
@@ -3598,7 +3504,7 @@
         <v>332.34</v>
       </c>
       <c r="C7" t="n">
-        <v>567762</v>
+        <v>584894</v>
       </c>
       <c r="D7" t="n">
         <v>23</v>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3140,12 +3140,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6/8/2026 8:21:19</t>
+          <t>6/10/2026 18:07:46</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chun Chieh</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3155,22 +3155,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>17,132</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3180,39 +3180,39 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Committee Approval Required</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6/8/2026 11:26:59</t>
+          <t>6/10/2026 19:24:21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>10.36</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>4,204</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3234,22 +3234,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6/9/2026 6:28:24</t>
+          <t>6/10/2026 20:19:35</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3274,44 +3274,44 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6/9/2026 9:34:20</t>
+          <t>6/8/2026 11:26:59</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4,204</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3321,54 +3321,195 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Committee Approval Required</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>6/8/2026 8:21:19</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Chun Chieh</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>11.35</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>17,132</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>6/9/2026 18:31:22</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>Jeremy</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
         <is>
           <t>7.05</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
         <is>
           <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>6/9/2026 6:28:24</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>6/9/2026 9:34:20</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>10.30</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
@@ -3415,13 +3556,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>327.92</v>
+        <v>347.49</v>
       </c>
       <c r="C2" t="n">
         <v>68636</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -3501,13 +3642,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>332.34</v>
+        <v>351.91</v>
       </c>
       <c r="C7" t="n">
         <v>584894</v>
       </c>
       <c r="D7" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,102 +465,390 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-25 16:56:39</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>29,156</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Healthy 365</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-25 18:37:29</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7.57</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-25 18:46:04</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5.63</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:21:27</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:35:55</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:23:38</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5.72</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-28 18:44:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7.06</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-29 17:48:24</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5.93</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Strava App</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-29 18:09:22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -570,7 +858,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -585,7 +873,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin Forerunner 265</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -595,19 +883,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-29 19:25:41</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -617,7 +905,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -632,7 +920,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -649,12 +937,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-30 10:55:11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -664,7 +952,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -679,7 +967,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Southwest</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -696,12 +984,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18 20:08:08</t>
+          <t>2026-05-30 20:44:11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -711,7 +999,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -726,7 +1014,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -743,22 +1031,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-31 20:24:34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -773,7 +1061,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -790,12 +1078,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-19 11:51:47</t>
+          <t>2026-05-31 21:59:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -810,7 +1098,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>105,386</t>
+          <t>60,056</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -820,7 +1108,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -837,27 +1125,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-06-01 09:09:44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44,238</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -867,7 +1155,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>fitness app</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -884,27 +1172,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-06-02 15:45:53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51,942</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -931,27 +1219,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-06-02 15:46:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Chee</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69,621</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -961,7 +1249,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Healthy 365</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -976,390 +1264,102 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-05-20 19:07:24</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-05-20 19:19:30</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>3.02</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-05-21 18:56:16</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-05-22 08:02:19</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Kai Fong</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>3.99</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-05-23 14:39:30</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>5.02</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-05-23 18:20:55</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>7.44</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>3,390</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-05-25 16:56:39</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CRX</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>29,156</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Healthy 365</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-05-25 18:37:29</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>7.57</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-25 18:46:04</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1394,19 +1394,19 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-26 14:21:27</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1448,12 +1448,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-27 09:35:55</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1495,12 +1495,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-27 18:23:38</t>
+          <t>2026-05-18 20:08:08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1542,22 +1542,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-28 18:44:00</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1589,27 +1589,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-29 17:48:24</t>
+          <t>2026-05-19 11:51:47</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105,386</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Strava App</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1636,12 +1636,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-29 18:09:22</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Garmin Forerunner 265</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1683,7 +1683,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:41</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1730,12 +1730,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-30 10:55:11</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Southwest</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1777,12 +1777,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-30 20:44:11</t>
+          <t>2026-05-20 19:07:24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1824,22 +1824,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-31 20:24:34</t>
+          <t>2026-05-20 19:19:30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1871,27 +1871,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-31 21:59:28</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>60,056</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1918,27 +1918,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01 09:09:44</t>
+          <t>2026-05-22 08:02:19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>44,238</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>fitness app</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1965,27 +1965,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-02 15:45:53</t>
+          <t>2026-05-23 14:39:30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>51,942</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2012,27 +2012,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-02 15:46:13</t>
+          <t>2026-05-23 18:20:55</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chee</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>69,621</t>
+          <t>3,390</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Healthy 365</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3281,32 +3281,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6/8/2026 11:26:59</t>
+          <t>6/11/2026 19:07:45</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>4,204</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3328,12 +3328,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6/8/2026 8:21:19</t>
+          <t>6/11/2026 19:31:48</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chun Chieh</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3343,22 +3343,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>17,132</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3368,19 +3368,19 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6/9/2026 18:31:22</t>
+          <t>6/12/2026 7:52:55</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3415,29 +3415,29 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6/9/2026 6:28:24</t>
+          <t>6/12/2026 8:57:56</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3469,45 +3469,280 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>6/12/2026 9:52:56</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>10.22</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>6/8/2026 11:26:59</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Surya</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>4,204</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>6/8/2026 8:21:19</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Chun Chieh</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>11.35</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>17,132</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6/9/2026 18:31:22</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>6/9/2026 6:28:24</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>6/9/2026 9:34:20</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Kelvin</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
         <is>
           <t>10.30</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Garmin</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
         <is>
           <t>Flagged</t>
         </is>
@@ -3556,13 +3791,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>347.49</v>
+        <v>386.73</v>
       </c>
       <c r="C2" t="n">
         <v>68636</v>
       </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -3642,13 +3877,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>351.91</v>
+        <v>391.15</v>
       </c>
       <c r="C7" t="n">
         <v>584894</v>
       </c>
       <c r="D7" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Strides_in_Sync_2026_Compilation.xlsx
+++ b/Strides_in_Sync_2026_Compilation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,390 +465,102 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-25 16:56:39</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CRX</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>29,156</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Healthy 365</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-25 18:37:29</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>7.57</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-25 18:46:04</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kai Fong</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5.63</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-26 14:21:27</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-27 09:35:55</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>7.56</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-27 18:23:38</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kai Fong</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>5.72</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-05-28 18:44:00</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>7.06</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-05-29 17:48:24</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Kai Fong</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>5.93</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Strava App</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-29 18:09:22</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -858,7 +570,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -873,7 +585,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Garmin Forerunner 265</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -883,19 +595,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:41</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -905,7 +617,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -920,7 +632,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -937,12 +649,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-30 10:55:11</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -952,7 +664,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -967,7 +679,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Southwest</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -984,12 +696,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-30 20:44:11</t>
+          <t>2026-05-18 20:08:08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -999,7 +711,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1014,7 +726,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1031,22 +743,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-31 20:24:34</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1061,7 +773,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1078,12 +790,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-31 21:59:28</t>
+          <t>2026-05-19 11:51:47</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1098,7 +810,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>60,056</t>
+          <t>105,386</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1108,7 +820,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1125,27 +837,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-01 09:09:44</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>44,238</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1155,7 +867,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>fitness app</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1172,27 +884,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-02 15:45:53</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>51,942</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1219,147 +931,435 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-02 15:46:13</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chee</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6.03</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-20 19:07:24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-20 19:19:30</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:56:16</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-22 08:02:19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:39:30</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>5.02</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-23 18:20:55</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>7.44</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3,390</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-25 16:56:39</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>69,621</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>29,156</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>Healthy 365</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-25 18:37:29</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7.57</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-25 18:46:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1394,19 +1394,19 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-26 14:21:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1448,12 +1448,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-27 09:35:55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1495,12 +1495,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-18 20:08:08</t>
+          <t>2026-05-27 18:23:38</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1542,22 +1542,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-28 18:44:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1589,27 +1589,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-19 11:51:47</t>
+          <t>2026-05-29 17:48:24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>105,386</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Strava App</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1636,12 +1636,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-29 18:09:22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin Forerunner 265</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1683,7 +1683,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-05-29 19:25:41</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1730,12 +1730,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-05-30 10:55:11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Southwest</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1777,12 +1777,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-20 19:07:24</t>
+          <t>2026-05-30 20:44:11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1824,22 +1824,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-20 19:19:30</t>
+          <t>2026-05-31 20:24:34</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1871,27 +1871,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-31 21:59:28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60,056</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1918,27 +1918,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-22 08:02:19</t>
+          <t>2026-06-01 09:09:44</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44,238</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>fitness app</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1965,27 +1965,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-23 14:39:30</t>
+          <t>2026-06-02 15:45:53</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51,942</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2012,27 +2012,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-06-02 15:46:13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Chee</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3,390</t>
+          <t>69,621</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Healthy 365</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3375,12 +3375,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6/12/2026 7:52:55</t>
+          <t>6/12/2026 19:21:35</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3415,19 +3415,19 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Committee Approval Required</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6/12/2026 8:57:56</t>
+          <t>6/12/2026 7:52:55</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3462,19 +3462,19 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6/12/2026 9:52:56</t>
+          <t>6/12/2026 8:57:56</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3516,32 +3516,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6/8/2026 11:26:59</t>
+          <t>6/12/2026 9:52:56</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>4,204</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3563,27 +3563,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6/8/2026 8:21:19</t>
+          <t>6/8/2026 11:26:59</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Chun Chieh</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>17,132</t>
+          <t>4,204</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3603,19 +3603,19 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Committee Approval Required</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6/9/2026 18:31:22</t>
+          <t>6/8/2026 8:21:19</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Chun Chieh</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3625,22 +3625,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17,132</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3650,29 +3650,29 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6/9/2026 6:28:24</t>
+          <t>6/9/2026 18:31:22</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3704,45 +3704,92 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>6/9/2026 6:28:24</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>6/9/2026 9:34:20</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>Kelvin</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
         <is>
           <t>10.30</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Garmin</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
         <is>
           <t>Flagged</t>
         </is>
@@ -3791,13 +3838,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>386.73</v>
+        <v>394.17</v>
       </c>
       <c r="C2" t="n">
         <v>68636</v>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -3877,13 +3924,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>391.15</v>
+        <v>398.59</v>
       </c>
       <c r="C7" t="n">
         <v>584894</v>
       </c>
       <c r="D7" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
